--- a/geçmiş yıllar data.xlsx
+++ b/geçmiş yıllar data.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\pasta sipariş app çalışma\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\python\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7635" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7635" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="2024" sheetId="1" r:id="rId1"/>
     <sheet name="2025" sheetId="2" r:id="rId2"/>
+    <sheet name="2026" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="2">
   <si>
     <t>Tarih</t>
   </si>
@@ -1091,4 +1092,402 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B48"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B2">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B3">
+        <v>2093</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B4">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>46268</v>
+      </c>
+      <c r="B5">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>46269</v>
+      </c>
+      <c r="B6">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>46270</v>
+      </c>
+      <c r="B7">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>46271</v>
+      </c>
+      <c r="B8">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>46272</v>
+      </c>
+      <c r="B9">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>46273</v>
+      </c>
+      <c r="B10">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B11">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B12">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B13">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>46277</v>
+      </c>
+      <c r="B14">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>46278</v>
+      </c>
+      <c r="B15">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>46279</v>
+      </c>
+      <c r="B16">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B17">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B18">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>46282</v>
+      </c>
+      <c r="B19">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B20">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>46284</v>
+      </c>
+      <c r="B21">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B22">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B23">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B24">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B25">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B26">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>46290</v>
+      </c>
+      <c r="B27">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B28">
+        <v>2082</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B29">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B30">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B31">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B32">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B33">
+        <v>2303</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B34">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B35">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B36">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B37">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B38">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B39">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B40">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B41">
+        <v>2078</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>46305</v>
+      </c>
+      <c r="B42">
+        <v>2940</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>46306</v>
+      </c>
+      <c r="B43">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B44">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B45">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B46">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B47">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B48">
+        <v>2252</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/geçmiş yıllar data.xlsx
+++ b/geçmiş yıllar data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7635" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7635" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="2024" sheetId="1" r:id="rId1"/>
@@ -88,7 +88,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -100,6 +100,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -382,7 +385,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -646,7 +649,154 @@
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
+      <c r="A33" s="1">
+        <v>45597</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>45598</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>45599</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>45600</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>45601</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>45602</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>45603</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>45604</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>45605</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>45606</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>45607</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>45608</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>45609</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>45610</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>45611</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>45612</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>45613</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>45614</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>45615</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>45616</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>45617</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>45618</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>45619</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>45620</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>45621</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>45622</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>45623</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>45624</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>45625</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>45626</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -917,100 +1067,271 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="4"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="4"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="4"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="4"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="4"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="4"/>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="4"/>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="4"/>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="4"/>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="4"/>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="4"/>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="4"/>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="4"/>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="4"/>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="4"/>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="4"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="4"/>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="4"/>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="4"/>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="4"/>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="4"/>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="4"/>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" s="4"/>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" s="4"/>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="4"/>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="4"/>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" s="4"/>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" s="4"/>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" s="4"/>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="4"/>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
+        <v>45962</v>
+      </c>
+      <c r="B33" s="5">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="4">
+        <v>45963</v>
+      </c>
+      <c r="B34" s="5">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="4">
+        <v>45964</v>
+      </c>
+      <c r="B35" s="5">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="4">
+        <v>45965</v>
+      </c>
+      <c r="B36" s="5">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="4">
+        <v>45966</v>
+      </c>
+      <c r="B37" s="5">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="4">
+        <v>45967</v>
+      </c>
+      <c r="B38" s="5">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="4">
+        <v>45968</v>
+      </c>
+      <c r="B39" s="5">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="4">
+        <v>45969</v>
+      </c>
+      <c r="B40" s="5">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="4">
+        <v>45970</v>
+      </c>
+      <c r="B41" s="5">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="4">
+        <v>45971</v>
+      </c>
+      <c r="B42" s="5">
+        <f>659+730+591</f>
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="4">
+        <v>45972</v>
+      </c>
+      <c r="B43" s="5">
+        <f>618+694+539</f>
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="4">
+        <v>45973</v>
+      </c>
+      <c r="B44" s="5">
+        <f>543+624+455</f>
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="4">
+        <v>45974</v>
+      </c>
+      <c r="B45" s="5">
+        <f>500+539+424</f>
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="4">
+        <v>45975</v>
+      </c>
+      <c r="B46" s="5">
+        <f>591+597+478</f>
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="4">
+        <v>45976</v>
+      </c>
+      <c r="B47" s="5">
+        <f>765+780+578</f>
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="4">
+        <v>45977</v>
+      </c>
+      <c r="B48" s="5">
+        <f>619+693+493</f>
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="4">
+        <v>45978</v>
+      </c>
+      <c r="B49" s="5">
+        <f>439+516+438</f>
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="4">
+        <v>45979</v>
+      </c>
+      <c r="B50" s="6">
+        <f>417+499+432</f>
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="4">
+        <v>45980</v>
+      </c>
+      <c r="B51" s="6">
+        <f>414+493+452</f>
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="4">
+        <v>45981</v>
+      </c>
+      <c r="B52" s="6">
+        <f>477+599+566</f>
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="4">
+        <v>45982</v>
+      </c>
+      <c r="B53" s="6">
+        <f>453+591+547</f>
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="4">
+        <v>45983</v>
+      </c>
+      <c r="B54" s="6">
+        <f>520+718+758</f>
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="4">
+        <v>45984</v>
+      </c>
+      <c r="B55" s="6">
+        <f>504+722+748</f>
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="4">
+        <v>45985</v>
+      </c>
+      <c r="B56" s="6">
+        <f>540+828+716</f>
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="4">
+        <v>45986</v>
+      </c>
+      <c r="B57" s="6">
+        <f>408+559+562</f>
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="4">
+        <v>45987</v>
+      </c>
+      <c r="B58" s="6">
+        <f>435+534+438</f>
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="4">
+        <v>45988</v>
+      </c>
+      <c r="B59" s="6">
+        <f>376+496+419</f>
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="4">
+        <v>45989</v>
+      </c>
+      <c r="B60" s="6">
+        <f>425+526+517</f>
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="4">
+        <v>45990</v>
+      </c>
+      <c r="B61" s="6">
+        <f>511+696+665</f>
+        <v>1872</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="4">
+        <v>45991</v>
+      </c>
+      <c r="B62" s="6">
+        <f>463+606+624</f>
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="4"/>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="4"/>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
@@ -1096,7 +1417,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B93"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -1487,6 +1808,237 @@
         <v>2252</v>
       </c>
     </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>46312</v>
+      </c>
+      <c r="B49">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>46313</v>
+      </c>
+      <c r="B50">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>46317</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>46319</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>46320</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>46322</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>46324</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>46325</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>46329</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>46330</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>46331</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>46332</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>46333</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>46334</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>46335</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>46336</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>46337</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>46338</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>46339</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>46340</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>46341</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>46342</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <v>46343</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>46344</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>46345</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>46346</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>46347</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>46348</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>46349</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>46350</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>46351</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>46352</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>46353</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>46354</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>46355</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>46356</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/geçmiş yıllar data.xlsx
+++ b/geçmiş yıllar data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7635" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7635" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="2024" sheetId="1" r:id="rId1"/>
@@ -1813,7 +1813,7 @@
         <v>46312</v>
       </c>
       <c r="B49">
-        <v>2100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -1821,17 +1821,23 @@
         <v>46313</v>
       </c>
       <c r="B50">
-        <v>1938</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>46314</v>
       </c>
+      <c r="B51">
+        <v>1938</v>
+      </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>46315</v>
+      </c>
+      <c r="B52">
+        <v>1589</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">

--- a/geçmiş yıllar data.xlsx
+++ b/geçmiş yıllar data.xlsx
@@ -1844,6 +1844,9 @@
       <c r="A53" s="1">
         <v>46316</v>
       </c>
+      <c r="B53">
+        <v>2053</v>
+      </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="1">

--- a/geçmiş yıllar data.xlsx
+++ b/geçmiş yıllar data.xlsx
@@ -1852,6 +1852,9 @@
       <c r="A54" s="1">
         <v>46317</v>
       </c>
+      <c r="B54">
+        <v>1601</v>
+      </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="1">

--- a/geçmiş yıllar data.xlsx
+++ b/geçmiş yıllar data.xlsx
@@ -1860,6 +1860,9 @@
       <c r="A55" s="1">
         <v>46318</v>
       </c>
+      <c r="B55">
+        <v>1818</v>
+      </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="1">

--- a/geçmiş yıllar data.xlsx
+++ b/geçmiş yıllar data.xlsx
@@ -1868,15 +1868,24 @@
       <c r="A56" s="1">
         <v>46319</v>
       </c>
+      <c r="B56">
+        <v>1886</v>
+      </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>46320</v>
       </c>
+      <c r="B57">
+        <v>2206</v>
+      </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>46321</v>
+      </c>
+      <c r="B58">
+        <v>2160</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">

--- a/geçmiş yıllar data.xlsx
+++ b/geçmiş yıllar data.xlsx
@@ -1892,6 +1892,9 @@
       <c r="A59" s="1">
         <v>46322</v>
       </c>
+      <c r="B59">
+        <v>1582</v>
+      </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="1">

--- a/geçmiş yıllar data.xlsx
+++ b/geçmiş yıllar data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7635" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7635"/>
   </bookViews>
   <sheets>
     <sheet name="2024" sheetId="1" r:id="rId1"/>
@@ -648,154 +648,244 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>45597</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B33">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>45598</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B34">
+        <v>2074</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>45599</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B35">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>45600</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B36">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>45601</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B37">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>45602</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B38">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>45603</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B39">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>45604</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B40">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>45605</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B41">
+        <v>2315</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>45606</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B42">
+        <v>2623</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>45607</v>
       </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B43">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>45608</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B44">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>45609</v>
       </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B45">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45610</v>
       </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B46">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>45611</v>
       </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B47">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>45612</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B48">
+        <v>2305</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>45613</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B49">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>45614</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B50">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>45615</v>
       </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B51">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>45616</v>
       </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B52">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>45617</v>
       </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B53">
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>45618</v>
       </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B54">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>45619</v>
       </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B55">
+        <v>2313</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>45620</v>
       </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B56">
+        <v>2607</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>45621</v>
       </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B57">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>45622</v>
       </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B58">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>45623</v>
       </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B59">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>45624</v>
       </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B60">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>45625</v>
       </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B61">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>45626</v>
+      </c>
+      <c r="B62">
+        <v>2165</v>
       </c>
     </row>
   </sheetData>

--- a/geçmiş yıllar data.xlsx
+++ b/geçmiş yıllar data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7635"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7635" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="2024" sheetId="1" r:id="rId1"/>
@@ -1990,6 +1990,9 @@
       <c r="A60" s="1">
         <v>46323</v>
       </c>
+      <c r="B60">
+        <v>1592</v>
+      </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="1">

--- a/geçmiş yıllar data.xlsx
+++ b/geçmiş yıllar data.xlsx
@@ -1998,6 +1998,9 @@
       <c r="A61" s="1">
         <v>46324</v>
       </c>
+      <c r="B61">
+        <v>2016</v>
+      </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
